--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.24291606600346</v>
+        <v>6.864473860725562</v>
       </c>
       <c r="D2" t="n">
-        <v>42.24291606600346</v>
+        <v>6.864473860725562</v>
       </c>
       <c r="E2" t="n">
-        <v>11.17479860103356</v>
+        <v>1.815904772667954</v>
       </c>
       <c r="F2" t="n">
-        <v>9.879015510161969</v>
+        <v>1.60534002040132</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.32425093803057</v>
+        <v>7.365190777429968</v>
       </c>
       <c r="D3" t="n">
-        <v>20.21156219823032</v>
+        <v>3.284378857212428</v>
       </c>
       <c r="E3" t="n">
-        <v>11.17479860103356</v>
+        <v>1.815904772667954</v>
       </c>
       <c r="F3" t="n">
-        <v>9.879015510161969</v>
+        <v>1.60534002040132</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.93888603715192</v>
+        <v>5.352568981037188</v>
       </c>
       <c r="D4" t="n">
-        <v>32.93269180627679</v>
+        <v>5.351562418519979</v>
       </c>
       <c r="E4" t="n">
-        <v>11.17479860103356</v>
+        <v>1.815904772667954</v>
       </c>
       <c r="F4" t="n">
-        <v>9.879015510161969</v>
+        <v>1.60534002040132</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.17290089230103</v>
+        <v>2.790596394998917</v>
       </c>
       <c r="D5" t="n">
-        <v>17.33099965737195</v>
+        <v>2.816287444322942</v>
       </c>
       <c r="E5" t="n">
-        <v>11.17479860103356</v>
+        <v>1.815904772667954</v>
       </c>
       <c r="F5" t="n">
-        <v>9.879015510161969</v>
+        <v>1.60534002040132</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.67023505157768</v>
+        <v>3.846413195881373</v>
       </c>
       <c r="D6" t="n">
-        <v>24.14982949178932</v>
+        <v>3.924347292415765</v>
       </c>
       <c r="E6" t="n">
-        <v>11.17479860103356</v>
+        <v>1.815904772667954</v>
       </c>
       <c r="F6" t="n">
-        <v>9.879015510161969</v>
+        <v>1.60534002040132</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.01479629319118</v>
+        <v>2.764904397643567</v>
       </c>
       <c r="D7" t="n">
-        <v>17.13826475457078</v>
+        <v>2.784968022617753</v>
       </c>
       <c r="E7" t="n">
-        <v>11.17479860103356</v>
+        <v>1.815904772667954</v>
       </c>
       <c r="F7" t="n">
-        <v>9.879015510161969</v>
+        <v>1.60534002040132</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.237187261349453</v>
+        <v>1.338542929969286</v>
       </c>
       <c r="D8" t="n">
-        <v>7.803089511153447</v>
+        <v>1.268002045562435</v>
       </c>
       <c r="E8" t="n">
-        <v>11.17479860103356</v>
+        <v>1.815904772667954</v>
       </c>
       <c r="F8" t="n">
-        <v>9.879015510161969</v>
+        <v>1.60534002040132</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.15341285360018</v>
+        <v>3.599929588710029</v>
       </c>
       <c r="D9" t="n">
-        <v>22.32980530435515</v>
+        <v>3.628593361957712</v>
       </c>
       <c r="E9" t="n">
-        <v>11.17479860103356</v>
+        <v>1.815904772667954</v>
       </c>
       <c r="F9" t="n">
-        <v>9.879015510161969</v>
+        <v>1.60534002040132</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.92795883745719</v>
+        <v>3.075793311086794</v>
       </c>
       <c r="D10" t="n">
-        <v>7.612520984992423</v>
+        <v>1.237034660061269</v>
       </c>
       <c r="E10" t="n">
-        <v>11.17479860103356</v>
+        <v>1.815904772667954</v>
       </c>
       <c r="F10" t="n">
-        <v>9.879015510161969</v>
+        <v>1.60534002040132</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.76934782742048</v>
+        <v>2.075019021955828</v>
       </c>
       <c r="D11" t="n">
-        <v>13.19908329892763</v>
+        <v>2.14485103607574</v>
       </c>
       <c r="E11" t="n">
-        <v>11.17479860103356</v>
+        <v>1.815904772667954</v>
       </c>
       <c r="F11" t="n">
-        <v>9.879015510161969</v>
+        <v>1.60534002040132</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.27307082802148</v>
+        <v>3.456874009553491</v>
       </c>
       <c r="D12" t="n">
-        <v>14.99308290799347</v>
+        <v>2.436375972548939</v>
       </c>
       <c r="E12" t="n">
-        <v>11.17479860103356</v>
+        <v>1.815904772667954</v>
       </c>
       <c r="F12" t="n">
-        <v>9.879015510161969</v>
+        <v>1.60534002040132</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
